--- a/artfynd/A 22382-2022 artfynd.xlsx
+++ b/artfynd/A 22382-2022 artfynd.xlsx
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
+          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 22382-2022 artfynd.xlsx
+++ b/artfynd/A 22382-2022 artfynd.xlsx
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Maria Hedenström, Ann-Christine Borja, Monika Norberg</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja, Maria Hedenström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 22382-2022 artfynd.xlsx
+++ b/artfynd/A 22382-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048969</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528299</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119526995</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048968</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,8 +1841,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528550</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22382-2022 artfynd.xlsx
+++ b/artfynd/A 22382-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135048969</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135034733</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135048966</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135048968</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22382-2022 artfynd.xlsx
+++ b/artfynd/A 22382-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135048969</v>
       </c>
       <c r="B2" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135034733</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
